--- a/artfynd/A 44412-2026 artfynd.xlsx
+++ b/artfynd/A 44412-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137282768</v>
       </c>
       <c r="B2" t="n">
-        <v>107958</v>
+        <v>107964</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>137282816</v>
       </c>
       <c r="B3" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
